--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95A2794-3876-D44E-8BB0-ACDF53970894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201D9322-BB54-1445-96BF-21E24D85794D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="900" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -179,6 +179,10 @@
   </si>
   <si>
     <t>PowderShop</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glue</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -493,7 +497,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -707,13 +711,13 @@
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -721,10 +725,10 @@
         <v>22</v>
       </c>
       <c r="B20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -732,10 +736,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -743,10 +747,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -754,21 +758,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -776,10 +780,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -787,21 +791,21 @@
         <v>30</v>
       </c>
       <c r="B26" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -809,10 +813,10 @@
         <v>34</v>
       </c>
       <c r="B28" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -820,10 +824,10 @@
         <v>34</v>
       </c>
       <c r="B29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -831,21 +835,21 @@
         <v>34</v>
       </c>
       <c r="B30" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B31" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -853,10 +857,10 @@
         <v>38</v>
       </c>
       <c r="B32" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -864,9 +868,20 @@
         <v>38</v>
       </c>
       <c r="B33" s="4">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="4">
         <v>3</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>41</v>
       </c>
     </row>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201D9322-BB54-1445-96BF-21E24D85794D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93B61BD-CF39-E643-8289-D7F598CB9814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13580" yWindow="1380" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -183,6 +183,25 @@
   </si>
   <si>
     <t>Glue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryTabType</t>
+  </si>
+  <si>
+    <t>InventoryTabType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -497,7 +516,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -885,6 +904,39 @@
         <v>41</v>
       </c>
     </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="8">
+        <v>2</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="8">
+        <v>3</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93B61BD-CF39-E643-8289-D7F598CB9814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E95770-CABB-7746-A111-29293C06FEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13580" yWindow="1380" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="920" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -202,6 +202,22 @@
   </si>
   <si>
     <t>Quest</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactSkin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerRecovery</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarRecovery</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColoredPowder</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -243,7 +259,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,6 +275,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -298,6 +320,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -516,7 +539,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -741,199 +764,254 @@
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B21" s="4">
-        <v>2</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>25</v>
+        <v>5</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B22" s="4">
-        <v>3</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>24</v>
+        <v>6</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>4</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B24" s="4">
-        <v>5</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4">
         <v>2</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4">
         <v>3</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B28" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B29" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B33" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4">
+        <v>3</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4">
+        <v>4</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="4">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4">
+        <v>3</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B40" s="8">
         <v>1</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="4" t="s">
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B41" s="8">
         <v>2</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C41" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="4" t="s">
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B42" s="8">
         <v>3</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>47</v>
       </c>
     </row>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E95770-CABB-7746-A111-29293C06FEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5BC643-1856-8C47-A6BB-050878D14C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40" yWindow="920" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -218,6 +218,18 @@
   </si>
   <si>
     <t>ColoredPowder</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinigameType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowderPortal</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -259,7 +271,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,6 +294,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2CD"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -321,6 +339,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -539,7 +558,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -1015,6 +1034,37 @@
         <v>47</v>
       </c>
     </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="8"/>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="10"/>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="10"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5BC643-1856-8C47-A6BB-050878D14C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE93E59-F439-A542-AD48-98688B189148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40" yWindow="920" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -230,6 +230,10 @@
   </si>
   <si>
     <t>PowderPortal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowShopPopup</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +562,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -749,14 +753,14 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="8" t="s">
-        <v>17</v>
+      <c r="A17" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B17" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -764,10 +768,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -775,10 +779,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -786,10 +790,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -797,10 +801,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="4">
-        <v>5</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -808,10 +812,10 @@
         <v>17</v>
       </c>
       <c r="B22" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -819,10 +823,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -830,21 +834,21 @@
         <v>17</v>
       </c>
       <c r="B24" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B25" s="4">
-        <v>1</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -852,10 +856,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -863,10 +867,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -874,10 +878,10 @@
         <v>22</v>
       </c>
       <c r="B28" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -885,21 +889,21 @@
         <v>22</v>
       </c>
       <c r="B29" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B30" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -907,10 +911,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -918,21 +922,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -940,10 +944,10 @@
         <v>34</v>
       </c>
       <c r="B34" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -951,10 +955,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -962,21 +966,21 @@
         <v>34</v>
       </c>
       <c r="B36" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B37" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -984,10 +988,10 @@
         <v>38</v>
       </c>
       <c r="B38" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -995,32 +999,32 @@
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4">
+        <v>3</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="8">
-        <v>1</v>
-      </c>
-      <c r="C40" s="8" t="s">
+      <c r="B41" s="8">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="8">
-        <v>2</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1028,21 +1032,21 @@
         <v>43</v>
       </c>
       <c r="B42" s="8">
+        <v>2</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="8">
         <v>3</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1050,20 +1054,31 @@
         <v>52</v>
       </c>
       <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="4">
         <v>2</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="8"/>
-    </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="10"/>
+      <c r="A46" s="8"/>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE93E59-F439-A542-AD48-98688B189148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3D6447-5FEB-CB42-87F0-C2FA4BB7D867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="920" windowWidth="21600" windowHeight="12200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15960" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="58">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -182,10 +182,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Glue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>InventoryTabType</t>
   </si>
   <si>
@@ -205,22 +201,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ArtifactSkin</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerRecovery</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FamiliarRecovery</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColoredPowder</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MinigameType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -235,6 +215,28 @@
   <si>
     <t>ShowShopPopup</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerHpRecovery</t>
+  </si>
+  <si>
+    <t>FamiliarHpRecovery</t>
+  </si>
+  <si>
+    <t>FamiliarTiredRecovery</t>
+  </si>
+  <si>
+    <t>RefinedMaterial</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest</t>
+  </si>
+  <si>
+    <t>Ride</t>
+  </si>
+  <si>
+    <t>FamiliarCall</t>
   </si>
 </sst>
 </file>
@@ -562,7 +564,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -760,7 +762,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -793,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -804,7 +806,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -814,8 +816,8 @@
       <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>49</v>
+      <c r="C22" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -826,7 +828,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -837,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -847,41 +849,41 @@
       <c r="B25" s="4">
         <v>8</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>25</v>
+      <c r="C25" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B26" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B27" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B28" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -889,10 +891,10 @@
         <v>22</v>
       </c>
       <c r="B29" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -900,76 +902,76 @@
         <v>22</v>
       </c>
       <c r="B30" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B33" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B34" s="4">
         <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B35" s="4">
         <v>2</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B36" s="4">
         <v>3</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -977,108 +979,141 @@
         <v>34</v>
       </c>
       <c r="B37" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B38" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B39" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="8">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4">
         <v>1</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>45</v>
+      <c r="C41" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="8">
+      <c r="A42" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="4">
         <v>2</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>46</v>
+      <c r="C42" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="4">
         <v>3</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>47</v>
+      <c r="C43" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8">
         <v>1</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="4">
+      <c r="A45" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="8">
         <v>2</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="8"/>
+      <c r="A46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="8">
+        <v>3</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="10"/>
+      <c r="A47" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="10"/>
+      <c r="A48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="8"/>
+    </row>
+    <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="10"/>
+    </row>
+    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3D6447-5FEB-CB42-87F0-C2FA4BB7D867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20773C80-9952-2442-ADB0-D63B8F43BF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15960" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7480" yWindow="1000" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="69">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -237,13 +237,244 @@
   </si>
   <si>
     <t>FamiliarCall</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솔라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화폐</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>마도구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복약</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>local_string;[EnumName][Id]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정제된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재료</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소환</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -276,8 +507,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,8 +559,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -330,11 +587,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -346,6 +618,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -564,19 +841,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
-        <v>1</v>
+      <c r="D1" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -754,7 +1032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -765,7 +1043,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>17</v>
       </c>
@@ -775,8 +1053,11 @@
       <c r="C18" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
@@ -786,8 +1067,11 @@
       <c r="C19" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>17</v>
       </c>
@@ -797,8 +1081,11 @@
       <c r="C20" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D20" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>17</v>
       </c>
@@ -808,8 +1095,11 @@
       <c r="C21" s="7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D21" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>17</v>
       </c>
@@ -819,8 +1109,11 @@
       <c r="C22" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D22" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>17</v>
       </c>
@@ -830,8 +1123,11 @@
       <c r="C23" s="9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>17</v>
       </c>
@@ -841,8 +1137,11 @@
       <c r="C24" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D24" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>17</v>
       </c>
@@ -852,8 +1151,11 @@
       <c r="C25" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D25" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>17</v>
       </c>
@@ -863,8 +1165,11 @@
       <c r="C26" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D26" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>17</v>
       </c>
@@ -874,71 +1179,74 @@
       <c r="C27" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D27" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B28" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B33" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -946,10 +1254,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -957,21 +1265,21 @@
         <v>30</v>
       </c>
       <c r="B35" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B36" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -979,10 +1287,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -990,10 +1298,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1001,21 +1309,21 @@
         <v>34</v>
       </c>
       <c r="B39" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B40" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1023,10 +1331,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1034,32 +1342,32 @@
         <v>38</v>
       </c>
       <c r="B42" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="4">
-        <v>3</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="B43" s="8">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="8" t="s">
-        <v>43</v>
+      <c r="A44" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="B44" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1067,21 +1375,21 @@
         <v>42</v>
       </c>
       <c r="B45" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="8">
-        <v>3</v>
+      <c r="A46" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1089,31 +1397,20 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="4">
-        <v>2</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>49</v>
-      </c>
+      <c r="A48" s="8"/>
     </row>
     <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="8"/>
+      <c r="A49" s="10"/>
     </row>
     <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
-    </row>
-    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20773C80-9952-2442-ADB0-D63B8F43BF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AD216E-9912-DD40-8A8C-38AA25F79079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7480" yWindow="1000" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7480" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -279,10 +279,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>local_string;[EnumName][Id]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -467,6 +463,10 @@
       </rPr>
       <t>소환</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>local_string;[EnumName][Order]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -846,7 +846,7 @@
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="21.5" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -854,7 +854,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1110,7 +1110,7 @@
         <v>53</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1124,7 +1124,7 @@
         <v>54</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1138,7 +1138,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1152,7 +1152,7 @@
         <v>55</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1166,7 +1166,7 @@
         <v>56</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1180,7 +1180,7 @@
         <v>57</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AD216E-9912-DD40-8A8C-38AA25F79079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A481D680-3EDB-1542-83C9-02B9A908D486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7480" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -467,6 +467,10 @@
   </si>
   <si>
     <t>local_string;[EnumName][Order]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CottonCandyShop</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -841,7 +845,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -1350,24 +1354,24 @@
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="4">
+        <v>4</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B44" s="8">
         <v>1</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C44" s="8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="8">
-        <v>2</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1375,21 +1379,21 @@
         <v>42</v>
       </c>
       <c r="B45" s="8">
+        <v>2</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="8">
         <v>3</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C46" s="8" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="4">
-        <v>1</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1397,20 +1401,31 @@
         <v>47</v>
       </c>
       <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4">
         <v>2</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="8"/>
-    </row>
     <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="10"/>
+      <c r="A49" s="8"/>
     </row>
     <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
+    </row>
+    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A481D680-3EDB-1542-83C9-02B9A908D486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827B17D0-5F0B-834C-943A-8A8EF42277E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7480" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="72">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -471,6 +471,14 @@
   </si>
   <si>
     <t>CottonCandyShop</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NpcMenuFunctionType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayCottonCandyMinigame</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -845,7 +853,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="4" customWidth="1"/>
@@ -971,14 +979,14 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
+      <c r="A11" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -986,10 +994,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -997,10 +1005,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1008,10 +1016,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="4">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1019,10 +1027,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="4">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1030,10 +1038,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="4">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1041,24 +1049,21 @@
         <v>10</v>
       </c>
       <c r="B17" s="4">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4">
         <v>7</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1066,13 +1071,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>59</v>
+        <v>18</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1080,13 +1085,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1094,13 +1099,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1108,13 +1113,13 @@
         <v>17</v>
       </c>
       <c r="B22" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1122,13 +1127,13 @@
         <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>6</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>54</v>
+        <v>5</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1136,13 +1141,13 @@
         <v>17</v>
       </c>
       <c r="B24" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1150,13 +1155,13 @@
         <v>17</v>
       </c>
       <c r="B25" s="4">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>55</v>
+        <v>7</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,13 +1169,13 @@
         <v>17</v>
       </c>
       <c r="B26" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1178,24 +1183,27 @@
         <v>17</v>
       </c>
       <c r="B27" s="4">
+        <v>9</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="4">
         <v>10</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1203,10 +1211,10 @@
         <v>22</v>
       </c>
       <c r="B29" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1214,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="B30" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1225,10 +1233,10 @@
         <v>22</v>
       </c>
       <c r="B31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1236,21 +1244,21 @@
         <v>22</v>
       </c>
       <c r="B32" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B33" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1258,10 +1266,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1269,21 +1277,21 @@
         <v>30</v>
       </c>
       <c r="B35" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B36" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1291,10 +1299,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1302,10 +1310,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1313,21 +1321,21 @@
         <v>34</v>
       </c>
       <c r="B39" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1335,10 +1343,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1346,10 +1354,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1357,32 +1365,32 @@
         <v>38</v>
       </c>
       <c r="B43" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="4">
+        <v>4</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B45" s="8">
         <v>1</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8">
-        <v>2</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1390,21 +1398,21 @@
         <v>42</v>
       </c>
       <c r="B46" s="8">
+        <v>2</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="8">
         <v>3</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="4">
-        <v>1</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1412,20 +1420,31 @@
         <v>47</v>
       </c>
       <c r="B48" s="4">
+        <v>1</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4">
         <v>2</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C49" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="8"/>
-    </row>
-    <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="10"/>
-    </row>
-    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="8"/>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827B17D0-5F0B-834C-943A-8A8EF42277E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB24C4D-9765-CA46-B3E5-040DDB1FE9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7480" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="73">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -479,6 +479,10 @@
   </si>
   <si>
     <t>PlayCottonCandyMinigame</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CottonCandy</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1438,7 +1442,15 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="8"/>
+      <c r="A50" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="4">
+        <v>3</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>

--- a/excel/EnumData.xlsx
+++ b/excel/EnumData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB24C4D-9765-CA46-B3E5-040DDB1FE9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CD6A90-5773-2145-914B-233BF4A18D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7480" yWindow="680" windowWidth="13440" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
   <si>
     <t>EnumName</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -483,6 +483,26 @@
   </si>
   <si>
     <t>CottonCandy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스틱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>파우더</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>버블건</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그라인더</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>펜던트</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1210,7 +1230,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>22</v>
       </c>
@@ -1220,8 +1240,11 @@
       <c r="C29" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D29" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>22</v>
       </c>
@@ -1231,8 +1254,11 @@
       <c r="C30" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D30" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>22</v>
       </c>
@@ -1242,8 +1268,11 @@
       <c r="C31" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D31" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>22</v>
       </c>
@@ -1253,8 +1282,11 @@
       <c r="C32" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D32" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>22</v>
       </c>
@@ -1264,8 +1296,11 @@
       <c r="C33" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>30</v>
       </c>
@@ -1276,7 +1311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>30</v>
       </c>
@@ -1287,7 +1322,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>30</v>
       </c>
@@ -1298,7 +1333,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
@@ -1309,7 +1344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
         <v>34</v>
       </c>
@@ -1320,7 +1355,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>34</v>
       </c>
@@ -1331,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
         <v>34</v>
       </c>
@@ -1342,7 +1377,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
         <v>38</v>
       </c>
@@ -1353,7 +1388,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
         <v>38</v>
       </c>
@@ -1364,7 +1399,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
@@ -1375,7 +1410,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
         <v>38</v>
       </c>
@@ -1386,7 +1421,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
         <v>43</v>
       </c>
@@ -1397,7 +1432,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="4" t="s">
         <v>42</v>
       </c>
@@ -1408,7 +1443,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
         <v>42</v>
       </c>
@@ -1419,7 +1454,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
         <v>47</v>
       </c>
